--- a/data/batches.xlsx
+++ b/data/batches.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="125">
   <si>
     <t>Batch Name/Job Name</t>
   </si>
@@ -23,6 +23,9 @@
     <t>Schedule Name/ Job Group Name</t>
   </si>
   <si>
+    <t>Trigger Needed</t>
+  </si>
+  <si>
     <t>BatchEnrollmentSync</t>
   </si>
   <si>
@@ -32,6 +35,9 @@
     <t>benefits_daily_6am</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>BatchEligibilityLoad</t>
   </si>
   <si>
@@ -39,6 +45,9 @@
   </si>
   <si>
     <t>benefits_daily_8am</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>BatchDependentVerification</t>
@@ -763,15 +772,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -781,251 +791,319 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
       <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1033,15 +1111,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1051,251 +1130,319 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
